--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91486138</v>
+        <v>91486137</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>sydost Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638687.3735957907</v>
+        <v>638620</v>
       </c>
       <c r="R2" t="n">
-        <v>6667798.211797303</v>
+        <v>6667807</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,21 +743,11 @@
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,50 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91486137</v>
+        <v>91486138</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>sydost Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638620.0813741111</v>
+        <v>638687</v>
       </c>
       <c r="R3" t="n">
-        <v>6667807.141805212</v>
+        <v>6667798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,21 +855,11 @@
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,7 +876,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,12 +897,7 @@
         <v>91486139</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638687.3735957907</v>
+        <v>638687</v>
       </c>
       <c r="R4" t="n">
-        <v>6667798.211797303</v>
+        <v>6667798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,19 +967,9 @@
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-02-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,12 +1009,7 @@
         <v>91486128</v>
       </c>
       <c r="B5" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638646.5831074375</v>
+        <v>638647</v>
       </c>
       <c r="R5" t="n">
-        <v>6667912.396618423</v>
+        <v>6667912</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,19 +1078,9 @@
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-02-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,12 +1120,7 @@
         <v>91486127</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638680.0682320576</v>
+        <v>638680</v>
       </c>
       <c r="R6" t="n">
-        <v>6667885.728533798</v>
+        <v>6667886</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,19 +1190,9 @@
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-02-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91486137</v>
+        <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>sydost Bråboda mosse, Upl</t>
+          <t>Hörnet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638620</v>
+        <v>638529</v>
       </c>
       <c r="R2" t="n">
-        <v>6667807</v>
+        <v>6667888</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,81 +771,66 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91486137</t>
+          <t>https://artportalen.se/Sighting/136177263</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91486138</v>
+        <v>91486137</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>sydost Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638687</v>
+        <v>638620</v>
       </c>
       <c r="R3" t="n">
-        <v>6667798</v>
+        <v>6667807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -903,59 +898,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91486138</t>
+          <t>https://artportalen.se/Sighting/91486137</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91486139</v>
+        <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>sydost Bråboda mosse, Upl</t>
+          <t>Hörnet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638687</v>
+        <v>638653</v>
       </c>
       <c r="R4" t="n">
-        <v>6667798</v>
+        <v>6667761</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,83 +995,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91486139</t>
+          <t>https://artportalen.se/Sighting/136177255</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91486128</v>
+        <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>6274</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105336</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>sydost Bråboda mosse, Upl</t>
+          <t>Hörnet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638647</v>
+        <v>638640</v>
       </c>
       <c r="R5" t="n">
-        <v>6667912</v>
+        <v>6667712</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,84 +1107,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>brunmurken granlåga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91486128</t>
+          <t>https://artportalen.se/Sighting/136177257</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91486127</v>
+        <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>101326</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>sydost Bråboda mosse, Upl</t>
+          <t>Hörnet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638680</v>
+        <v>638624</v>
       </c>
       <c r="R6" t="n">
-        <v>6667886</v>
+        <v>6667807</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,12 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1219,1497 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136177260</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136177262</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>638522</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6667854</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177262</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136177264</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92739</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>638628</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6667907</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177264</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136177251</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96506</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>638684</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6667806</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177251</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136177266</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96506</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>638671</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6667896</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177266</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136177250</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>638596</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6667808</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177250</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>91486138</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>sydost Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>638687</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6667798</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91486138</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>91486139</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>sydost Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>638687</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6667798</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91486139</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136177258</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>638640</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6667712</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177258</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>91486128</v>
+      </c>
+      <c r="B15" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>sydost Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>638647</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6667912</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>brunmurken granlåga</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91486128</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136177259</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>638599</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6667742</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177259</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>91486127</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>sydost Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>638680</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6667886</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/91486127</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136177256</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101504</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>638659</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6667730</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177256</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136177265</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101504</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hörnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>638673</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6667898</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177265</t>
         </is>
       </c>
     </row>
@@ -1259,6 +2720,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92739</v>
+        <v>92740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92740</v>
+        <v>92741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136177250</v>
       </c>
       <c r="B11" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136177250</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92747</v>
+        <v>92748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136177250</v>
       </c>
       <c r="B11" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136177250</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92761</v>
+        <v>92762</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92762</v>
+        <v>92775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136177250</v>
       </c>
       <c r="B11" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92775</v>
+        <v>92776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136177251</v>
       </c>
       <c r="B9" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136177266</v>
       </c>
       <c r="B10" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>136177256</v>
       </c>
       <c r="B18" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136177265</v>
       </c>
       <c r="B19" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
